--- a/results/4_nichevol_ouwieB.xlsx
+++ b/results/4_nichevol_ouwieB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/phgaem/Documents/Projetos/3_PhD/1_Project/Eugenia Biogeography/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{701DD4E3-7533-C64E-A617-9F94D38516FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA53266D-BFF0-5A4A-9BD5-052253D82528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4180" yWindow="-20980" windowWidth="38400" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -276,11 +276,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -621,10 +622,10 @@
         <v>0.36023864719999998</v>
       </c>
       <c r="C2">
-        <v>7.9395172306121004E-2</v>
+        <v>9.2924388211585995E-2</v>
       </c>
       <c r="D2">
-        <v>0.80193979760907996</v>
+        <v>0.61925506624399995</v>
       </c>
       <c r="E2">
         <v>-21.1128508</v>
@@ -650,10 +651,10 @@
         <v>0.18203737480000001</v>
       </c>
       <c r="C3">
-        <v>0.124499253691956</v>
+        <v>7.2800595293980003E-2</v>
       </c>
       <c r="D3">
-        <v>0.22866533174309001</v>
+        <v>0.30193598768796998</v>
       </c>
       <c r="E3">
         <v>-27.139579099999999</v>
@@ -679,10 +680,10 @@
         <v>0.12667812019999999</v>
       </c>
       <c r="C4">
-        <v>6.1341035689848999E-2</v>
+        <v>4.7403406227012002E-2</v>
       </c>
       <c r="D4">
-        <v>0.16818328490851001</v>
+        <v>0.19833213353554999</v>
       </c>
       <c r="E4">
         <v>-24.950091700000002</v>
@@ -708,10 +709,10 @@
         <v>0.1154433731</v>
       </c>
       <c r="C5">
-        <v>3.5922935722475999E-2</v>
+        <v>3.5098758391229001E-2</v>
       </c>
       <c r="D5">
-        <v>0.16656957429524</v>
+        <v>0.20947273141016001</v>
       </c>
       <c r="E5">
         <v>-17.171583800000001</v>
@@ -737,10 +738,10 @@
         <v>6.3186915100000005E-2</v>
       </c>
       <c r="C6">
-        <v>5.1186507587605998E-2</v>
+        <v>5.0637098868337997E-2</v>
       </c>
       <c r="D6">
-        <v>7.0633946708020007E-2</v>
+        <v>8.1916672282439998E-2</v>
       </c>
       <c r="E6">
         <v>-164.14429949999999</v>
@@ -766,10 +767,10 @@
         <v>5.4460592400000001E-2</v>
       </c>
       <c r="C7">
-        <v>4.7682435031160004E-3</v>
+        <v>2.5382514386719998E-3</v>
       </c>
       <c r="D7">
-        <v>8.2127160336519997E-2</v>
+        <v>0.12431101238651</v>
       </c>
       <c r="E7">
         <v>-7.1733048999999998</v>
@@ -795,10 +796,10 @@
         <v>5.2095723599999998E-2</v>
       </c>
       <c r="C8">
-        <v>1.2340173203666E-2</v>
+        <v>8.8161299689030002E-3</v>
       </c>
       <c r="D8">
-        <v>7.4621095692270004E-2</v>
+        <v>0.11831125312578</v>
       </c>
       <c r="E8">
         <v>-12.2219479</v>
@@ -824,10 +825,10 @@
         <v>5.0895610799999998E-2</v>
       </c>
       <c r="C9">
-        <v>2.1415725305762998E-2</v>
+        <v>1.4980808159591E-2</v>
       </c>
       <c r="D9">
-        <v>9.1444179017279997E-2</v>
+        <v>9.8795176158349998E-2</v>
       </c>
       <c r="E9">
         <v>-12.311692300000001</v>
@@ -853,10 +854,10 @@
         <v>3.7612128500000001E-2</v>
       </c>
       <c r="C10">
-        <v>2.4983206131087E-2</v>
+        <v>1.9086922727447001E-2</v>
       </c>
       <c r="D10">
-        <v>4.7342795010510003E-2</v>
+        <v>5.6416817005759998E-2</v>
       </c>
       <c r="E10">
         <v>-41.790501200000001</v>
@@ -882,10 +883,10 @@
         <v>2.3584138599999999E-2</v>
       </c>
       <c r="C11">
-        <v>1.2280563440346001E-2</v>
+        <v>1.1883062423364E-2</v>
       </c>
       <c r="D11">
-        <v>3.6494919523669997E-2</v>
+        <v>3.3701583574349998E-2</v>
       </c>
       <c r="E11">
         <v>-32.047401200000003</v>
@@ -911,10 +912,10 @@
         <v>2.2722195800000001E-2</v>
       </c>
       <c r="C12">
-        <v>1.4783536860345E-2</v>
+        <v>1.1273662088992E-2</v>
       </c>
       <c r="D12">
-        <v>2.969107773255E-2</v>
+        <v>3.8230505324170001E-2</v>
       </c>
       <c r="E12">
         <v>-32.9801109</v>
@@ -940,10 +941,10 @@
         <v>1.1574173999999999E-3</v>
       </c>
       <c r="C13">
-        <v>6.3204815951000001E-4</v>
+        <v>2.34232812551E-4</v>
       </c>
       <c r="D13">
-        <v>2.4009796033299998E-3</v>
+        <v>2.3948953840299998E-3</v>
       </c>
       <c r="E13">
         <v>-10.112675299999999</v>
@@ -969,10 +970,10 @@
         <v>9.5859063199999997E-2</v>
       </c>
       <c r="C14">
-        <v>7.9212503457837993E-2</v>
+        <v>7.6495495473291999E-2</v>
       </c>
       <c r="D14">
-        <v>0.10044005888775</v>
+        <v>0.12248829690528</v>
       </c>
       <c r="E14">
         <v>-166.02674060000001</v>
@@ -997,10 +998,10 @@
       <c r="B15">
         <v>4.8230710199999999E-2</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="4">
         <v>2.4173747091417001E-2</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="4">
         <v>6.1301956134210002E-2</v>
       </c>
       <c r="E15">
@@ -1026,11 +1027,11 @@
       <c r="B16">
         <v>4.5146741099999999E-2</v>
       </c>
-      <c r="C16">
-        <v>2.2208487708150999E-2</v>
-      </c>
-      <c r="D16">
-        <v>6.6104185258309994E-2</v>
+      <c r="C16" s="4">
+        <v>2.4964102219809998E-2</v>
+      </c>
+      <c r="D16" s="4">
+        <v>7.4486586023510007E-2</v>
       </c>
       <c r="E16">
         <v>-27.2778864</v>
@@ -1055,11 +1056,11 @@
       <c r="B17">
         <v>4.3112135900000001E-2</v>
       </c>
-      <c r="C17">
-        <v>1.4741032194841E-2</v>
-      </c>
-      <c r="D17">
-        <v>8.7391275291540005E-2</v>
+      <c r="C17" s="4">
+        <v>1.2256236113571999E-2</v>
+      </c>
+      <c r="D17" s="4">
+        <v>8.4430226636299996E-2</v>
       </c>
       <c r="E17">
         <v>-13.9003718</v>
@@ -1084,10 +1085,10 @@
       <c r="B18">
         <v>3.2889855199999998E-2</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="4">
         <v>8.1757669849019995E-3</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="4">
         <v>4.3801915616259998E-2</v>
       </c>
       <c r="E18">
@@ -1113,11 +1114,11 @@
       <c r="B19">
         <v>2.2039018099999998E-2</v>
       </c>
-      <c r="C19">
-        <v>6.894317224617E-3</v>
-      </c>
-      <c r="D19">
-        <v>3.088885946748E-2</v>
+      <c r="C19" s="4">
+        <v>5.077588706231E-3</v>
+      </c>
+      <c r="D19" s="4">
+        <v>4.8721127685680002E-2</v>
       </c>
       <c r="E19">
         <v>-12.9386808</v>
@@ -1142,11 +1143,11 @@
       <c r="B20">
         <v>1.43002514E-2</v>
       </c>
-      <c r="C20">
-        <v>5.1665043822259997E-3</v>
-      </c>
-      <c r="D20">
-        <v>1.7379494346530001E-2</v>
+      <c r="C20" s="4">
+        <v>6.548906495338E-3</v>
+      </c>
+      <c r="D20" s="4">
+        <v>2.0675037160840001E-2</v>
       </c>
       <c r="E20">
         <v>-10.0124456</v>
@@ -1171,11 +1172,11 @@
       <c r="B21">
         <v>9.0832685E-3</v>
       </c>
-      <c r="C21">
-        <v>5.1007631508529997E-3</v>
-      </c>
-      <c r="D21">
-        <v>1.0066062396280001E-2</v>
+      <c r="C21" s="4">
+        <v>5.4171082325289999E-3</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1.516065161086E-2</v>
       </c>
       <c r="E21">
         <v>-20.563210099999999</v>
@@ -1200,10 +1201,10 @@
       <c r="B22">
         <v>7.6773168999999999E-3</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="4">
         <v>1.4734712254979999E-3</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="4">
         <v>1.1108632893849999E-2</v>
       </c>
       <c r="E22">
@@ -1229,11 +1230,11 @@
       <c r="B23">
         <v>9.618246E-4</v>
       </c>
-      <c r="C23">
-        <v>2.9467870224000002E-4</v>
-      </c>
-      <c r="D23">
-        <v>1.3565291993000001E-3</v>
+      <c r="C23" s="4">
+        <v>1.8386840197599999E-4</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1.78193599399E-3</v>
       </c>
       <c r="E23">
         <v>-1.7045032</v>
@@ -1258,10 +1259,10 @@
       <c r="B24">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="4">
         <v>4.0130589999999999E-9</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="4">
         <v>2.0694410000000002E-8</v>
       </c>
       <c r="E24">
@@ -1287,10 +1288,10 @@
       <c r="B25">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="4">
         <v>1.722197E-9</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="4">
         <v>2.2477200000000001E-8</v>
       </c>
       <c r="E25">
@@ -1316,11 +1317,11 @@
       <c r="B26">
         <v>8.0778479799999997E-2</v>
       </c>
-      <c r="C26">
-        <v>2.2331915276163E-2</v>
-      </c>
-      <c r="D26">
-        <v>0.11138324810222</v>
+      <c r="C26" s="4">
+        <v>2.0300016669945999E-2</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0.16319783050848</v>
       </c>
       <c r="E26">
         <v>-15.7249345</v>
@@ -1345,11 +1346,11 @@
       <c r="B27">
         <v>4.3267708799999999E-2</v>
       </c>
-      <c r="C27">
-        <v>2.7833411486990998E-2</v>
-      </c>
-      <c r="D27">
-        <v>6.9822187429300006E-2</v>
+      <c r="C27" s="4">
+        <v>1.8040763896783E-2</v>
+      </c>
+      <c r="D27" s="4">
+        <v>7.0459083645339995E-2</v>
       </c>
       <c r="E27">
         <v>-18.878115699999999</v>
@@ -1374,11 +1375,11 @@
       <c r="B28">
         <v>4.1261413599999998E-2</v>
       </c>
-      <c r="C28">
-        <v>2.4696981802192E-2</v>
-      </c>
-      <c r="D28">
-        <v>6.4437388603770004E-2</v>
+      <c r="C28" s="4">
+        <v>2.4696981999999999E-2</v>
+      </c>
+      <c r="D28" s="4">
+        <v>6.4437388999999998E-2</v>
       </c>
       <c r="E28">
         <v>-34.920170200000001</v>
@@ -1403,11 +1404,11 @@
       <c r="B29">
         <v>4.0805280200000002E-2</v>
       </c>
-      <c r="C29">
-        <v>2.3354582704239998E-2</v>
-      </c>
-      <c r="D29">
-        <v>4.7626662598820001E-2</v>
+      <c r="C29" s="4">
+        <v>2.1236031439728999E-2</v>
+      </c>
+      <c r="D29" s="4">
+        <v>6.1968669191480003E-2</v>
       </c>
       <c r="E29">
         <v>-30.209830499999999</v>
@@ -1432,11 +1433,11 @@
       <c r="B30">
         <v>3.4681526499999997E-2</v>
       </c>
-      <c r="C30">
-        <v>2.5139631629544999E-2</v>
-      </c>
-      <c r="D30">
-        <v>3.9110358335919998E-2</v>
+      <c r="C30" s="4">
+        <v>2.5482472605873999E-2</v>
+      </c>
+      <c r="D30" s="4">
+        <v>4.466217695843E-2</v>
       </c>
       <c r="E30">
         <v>-118.8304881</v>
@@ -1461,10 +1462,10 @@
       <c r="B31">
         <v>3.0292582200000001E-2</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="4">
         <v>1.6894828959563998E-2</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="4">
         <v>4.6463034384290003E-2</v>
       </c>
       <c r="E31">
@@ -1491,10 +1492,10 @@
         <v>2.54332167E-2</v>
       </c>
       <c r="C32">
-        <v>1.4310686312835001E-2</v>
+        <v>1.3152388562103001E-2</v>
       </c>
       <c r="D32">
-        <v>3.8493363347429997E-2</v>
+        <v>3.8261493983390002E-2</v>
       </c>
       <c r="E32">
         <v>-23.770845099999999</v>
@@ -1520,10 +1521,10 @@
         <v>5.1519256000000001E-3</v>
       </c>
       <c r="C33">
-        <v>1.193928025041E-3</v>
+        <v>3.1459277569599999E-4</v>
       </c>
       <c r="D33">
-        <v>1.249608286267E-2</v>
+        <v>1.412406561186E-2</v>
       </c>
       <c r="E33">
         <v>-3.4303203</v>
@@ -1549,10 +1550,10 @@
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="C34">
-        <v>4.7451710000000004E-9</v>
+        <v>1.9633510000000002E-9</v>
       </c>
       <c r="D34">
-        <v>1.9929899999999998E-8</v>
+        <v>1.890716E-8</v>
       </c>
       <c r="E34">
         <v>-2.1261632000000001</v>
@@ -1578,10 +1579,10 @@
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="C35">
-        <v>2.467413E-9</v>
+        <v>2.4309120000000001E-9</v>
       </c>
       <c r="D35">
-        <v>1.536434E-8</v>
+        <v>2.3434440000000001E-8</v>
       </c>
       <c r="E35">
         <v>-5.8480487999999999</v>
@@ -1607,10 +1608,10 @@
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="C36">
-        <v>3.7159720000000002E-9</v>
+        <v>2.1359040000000001E-9</v>
       </c>
       <c r="D36">
-        <v>1.759472E-8</v>
+        <v>1.878628E-8</v>
       </c>
       <c r="E36">
         <v>1.5043422</v>
@@ -1636,10 +1637,10 @@
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="C37">
-        <v>4.7383189999999999E-9</v>
+        <v>3.6687219999999999E-9</v>
       </c>
       <c r="D37">
-        <v>1.3952719999999999E-8</v>
+        <v>1.7141230000000002E-8</v>
       </c>
       <c r="E37">
         <v>-5.4535860999999999</v>
@@ -1717,11 +1718,11 @@
       </c>
       <c r="D2" s="1">
         <f>ROUND('Sheet 1'!C2, 3)</f>
-        <v>7.9000000000000001E-2</v>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="E2" s="1">
         <f>ROUND('Sheet 1'!D2, 3)</f>
-        <v>0.80200000000000005</v>
+        <v>0.61899999999999999</v>
       </c>
       <c r="F2" s="1">
         <f>ROUND('Sheet 1'!E2, 3)</f>
@@ -1747,11 +1748,11 @@
       </c>
       <c r="D3" s="1">
         <f>ROUND('Sheet 1'!C3, 3)</f>
-        <v>0.124</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="E3" s="1">
         <f>ROUND('Sheet 1'!D3, 3)</f>
-        <v>0.22900000000000001</v>
+        <v>0.30199999999999999</v>
       </c>
       <c r="F3" s="1">
         <f>ROUND('Sheet 1'!E3, 3)</f>
@@ -1777,11 +1778,11 @@
       </c>
       <c r="D4" s="1">
         <f>ROUND('Sheet 1'!C4, 3)</f>
-        <v>6.0999999999999999E-2</v>
+        <v>4.7E-2</v>
       </c>
       <c r="E4" s="1">
         <f>ROUND('Sheet 1'!D4, 3)</f>
-        <v>0.16800000000000001</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="F4" s="1">
         <f>ROUND('Sheet 1'!E4, 3)</f>
@@ -1807,11 +1808,11 @@
       </c>
       <c r="D5" s="1">
         <f>ROUND('Sheet 1'!C5, 3)</f>
-        <v>3.5999999999999997E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="E5" s="1">
         <f>ROUND('Sheet 1'!D5, 3)</f>
-        <v>0.16700000000000001</v>
+        <v>0.20899999999999999</v>
       </c>
       <c r="F5" s="1">
         <f>ROUND('Sheet 1'!E5, 3)</f>
@@ -1841,7 +1842,7 @@
       </c>
       <c r="E6" s="1">
         <f>ROUND('Sheet 1'!D6, 3)</f>
-        <v>7.0999999999999994E-2</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="F6" s="1">
         <f>ROUND('Sheet 1'!E6, 3)</f>
@@ -1867,11 +1868,11 @@
       </c>
       <c r="D7" s="1">
         <f>ROUND('Sheet 1'!C7, 3)</f>
-        <v>5.0000000000000001E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="E7" s="1">
         <f>ROUND('Sheet 1'!D7, 3)</f>
-        <v>8.2000000000000003E-2</v>
+        <v>0.124</v>
       </c>
       <c r="F7" s="1">
         <f>ROUND('Sheet 1'!E7, 3)</f>
@@ -1897,11 +1898,11 @@
       </c>
       <c r="D8" s="1">
         <f>ROUND('Sheet 1'!C8, 3)</f>
-        <v>1.2E-2</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="E8" s="1">
         <f>ROUND('Sheet 1'!D8, 3)</f>
-        <v>7.4999999999999997E-2</v>
+        <v>0.11799999999999999</v>
       </c>
       <c r="F8" s="1">
         <f>ROUND('Sheet 1'!E8, 3)</f>
@@ -1927,11 +1928,11 @@
       </c>
       <c r="D9" s="1">
         <f>ROUND('Sheet 1'!C9, 3)</f>
-        <v>2.1000000000000001E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="E9" s="1">
         <f>ROUND('Sheet 1'!D9, 3)</f>
-        <v>9.0999999999999998E-2</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="F9" s="1">
         <f>ROUND('Sheet 1'!E9, 3)</f>
@@ -1957,11 +1958,11 @@
       </c>
       <c r="D10" s="1">
         <f>ROUND('Sheet 1'!C10, 3)</f>
-        <v>2.5000000000000001E-2</v>
+        <v>1.9E-2</v>
       </c>
       <c r="E10" s="1">
         <f>ROUND('Sheet 1'!D10, 3)</f>
-        <v>4.7E-2</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="F10" s="1">
         <f>ROUND('Sheet 1'!E10, 3)</f>
@@ -1991,7 +1992,7 @@
       </c>
       <c r="E11" s="1">
         <f>ROUND('Sheet 1'!D11, 3)</f>
-        <v>3.5999999999999997E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="F11" s="1">
         <f>ROUND('Sheet 1'!E11, 3)</f>
@@ -2017,11 +2018,11 @@
       </c>
       <c r="D12" s="1">
         <f>ROUND('Sheet 1'!C12, 3)</f>
-        <v>1.4999999999999999E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="E12" s="1">
         <f>ROUND('Sheet 1'!D12, 3)</f>
-        <v>0.03</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="F12" s="1">
         <f>ROUND('Sheet 1'!E12, 3)</f>
@@ -2047,7 +2048,7 @@
       </c>
       <c r="D13" s="1">
         <f>ROUND('Sheet 1'!C13, 3)</f>
-        <v>1E-3</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
         <f>ROUND('Sheet 1'!D13, 3)</f>
@@ -2079,11 +2080,11 @@
       </c>
       <c r="D14" s="1">
         <f>ROUND('Sheet 1'!C14, 3)</f>
-        <v>7.9000000000000001E-2</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="E14" s="1">
         <f>ROUND('Sheet 1'!D14, 3)</f>
-        <v>0.1</v>
+        <v>0.122</v>
       </c>
       <c r="F14" s="1">
         <f>ROUND('Sheet 1'!E14, 3)</f>
@@ -2139,11 +2140,11 @@
       </c>
       <c r="D16" s="1">
         <f>ROUND('Sheet 1'!C16, 3)</f>
-        <v>2.1999999999999999E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="E16" s="1">
         <f>ROUND('Sheet 1'!D16, 3)</f>
-        <v>6.6000000000000003E-2</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="F16" s="1">
         <f>ROUND('Sheet 1'!E16, 3)</f>
@@ -2169,11 +2170,11 @@
       </c>
       <c r="D17" s="1">
         <f>ROUND('Sheet 1'!C17, 3)</f>
-        <v>1.4999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="E17" s="1">
         <f>ROUND('Sheet 1'!D17, 3)</f>
-        <v>8.6999999999999994E-2</v>
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="F17" s="1">
         <f>ROUND('Sheet 1'!E17, 3)</f>
@@ -2229,11 +2230,11 @@
       </c>
       <c r="D19" s="1">
         <f>ROUND('Sheet 1'!C19, 3)</f>
-        <v>7.0000000000000001E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E19" s="1">
         <f>ROUND('Sheet 1'!D19, 3)</f>
-        <v>3.1E-2</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="F19" s="1">
         <f>ROUND('Sheet 1'!E19, 3)</f>
@@ -2259,11 +2260,11 @@
       </c>
       <c r="D20" s="1">
         <f>ROUND('Sheet 1'!C20, 3)</f>
-        <v>5.0000000000000001E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="E20" s="1">
         <f>ROUND('Sheet 1'!D20, 3)</f>
-        <v>1.7000000000000001E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="F20" s="1">
         <f>ROUND('Sheet 1'!E20, 3)</f>
@@ -2293,7 +2294,7 @@
       </c>
       <c r="E21" s="1">
         <f>ROUND('Sheet 1'!D21, 3)</f>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="F21" s="1">
         <f>ROUND('Sheet 1'!E21, 3)</f>
@@ -2349,11 +2350,11 @@
       </c>
       <c r="D23" s="2">
         <f>'Sheet 1'!C23</f>
-        <v>2.9467870224000002E-4</v>
+        <v>1.8386840197599999E-4</v>
       </c>
       <c r="E23" s="1">
         <f>ROUND('Sheet 1'!D23, 3)</f>
-        <v>1E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="F23" s="1">
         <f>ROUND('Sheet 1'!E23, 3)</f>
@@ -2441,11 +2442,11 @@
       </c>
       <c r="D26" s="1">
         <f>ROUND('Sheet 1'!C26, 3)</f>
-        <v>2.1999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E26" s="1">
         <f>ROUND('Sheet 1'!D26, 3)</f>
-        <v>0.111</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="F26" s="1">
         <f>ROUND('Sheet 1'!E26, 3)</f>
@@ -2471,7 +2472,7 @@
       </c>
       <c r="D27" s="1">
         <f>ROUND('Sheet 1'!C27, 3)</f>
-        <v>2.8000000000000001E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="E27" s="1">
         <f>ROUND('Sheet 1'!D27, 3)</f>
@@ -2531,11 +2532,11 @@
       </c>
       <c r="D29" s="1">
         <f>ROUND('Sheet 1'!C29, 3)</f>
-        <v>2.3E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="E29" s="1">
         <f>ROUND('Sheet 1'!D29, 3)</f>
-        <v>4.8000000000000001E-2</v>
+        <v>6.2E-2</v>
       </c>
       <c r="F29" s="1">
         <f>ROUND('Sheet 1'!E29, 3)</f>
@@ -2565,7 +2566,7 @@
       </c>
       <c r="E30" s="1">
         <f>ROUND('Sheet 1'!D30, 3)</f>
-        <v>3.9E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="F30" s="1">
         <f>ROUND('Sheet 1'!E30, 3)</f>
@@ -2621,7 +2622,7 @@
       </c>
       <c r="D32" s="1">
         <f>ROUND('Sheet 1'!C32, 3)</f>
-        <v>1.4E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="E32" s="1">
         <f>ROUND('Sheet 1'!D32, 3)</f>
@@ -2651,11 +2652,11 @@
       </c>
       <c r="D33" s="1">
         <f>ROUND('Sheet 1'!C33, 3)</f>
-        <v>1E-3</v>
+        <v>0</v>
       </c>
       <c r="E33" s="1">
         <f>ROUND('Sheet 1'!D33, 3)</f>
-        <v>1.2E-2</v>
+        <v>1.4E-2</v>
       </c>
       <c r="F33" s="1">
         <f>ROUND('Sheet 1'!E33, 3)</f>
@@ -2681,11 +2682,11 @@
       </c>
       <c r="D34" s="2">
         <f>'Sheet 1'!C34</f>
-        <v>4.7451710000000004E-9</v>
+        <v>1.9633510000000002E-9</v>
       </c>
       <c r="E34" s="2">
         <f>'Sheet 1'!D34</f>
-        <v>1.9929899999999998E-8</v>
+        <v>1.890716E-8</v>
       </c>
       <c r="F34" s="1">
         <f>ROUND('Sheet 1'!E34, 3)</f>
@@ -2711,11 +2712,11 @@
       </c>
       <c r="D35" s="2">
         <f>'Sheet 1'!C35</f>
-        <v>2.467413E-9</v>
+        <v>2.4309120000000001E-9</v>
       </c>
       <c r="E35" s="2">
         <f>'Sheet 1'!D35</f>
-        <v>1.536434E-8</v>
+        <v>2.3434440000000001E-8</v>
       </c>
       <c r="F35" s="1">
         <f>ROUND('Sheet 1'!E35, 3)</f>
@@ -2741,11 +2742,11 @@
       </c>
       <c r="D36" s="2">
         <f>'Sheet 1'!C36</f>
-        <v>3.7159720000000002E-9</v>
+        <v>2.1359040000000001E-9</v>
       </c>
       <c r="E36" s="2">
         <f>'Sheet 1'!D36</f>
-        <v>1.759472E-8</v>
+        <v>1.878628E-8</v>
       </c>
       <c r="F36" s="1">
         <f>ROUND('Sheet 1'!E36, 3)</f>
@@ -2771,11 +2772,11 @@
       </c>
       <c r="D37" s="2">
         <f>'Sheet 1'!C37</f>
-        <v>4.7383189999999999E-9</v>
+        <v>3.6687219999999999E-9</v>
       </c>
       <c r="E37" s="2">
         <f>'Sheet 1'!D37</f>
-        <v>1.3952719999999999E-8</v>
+        <v>1.7141230000000002E-8</v>
       </c>
       <c r="F37" s="1">
         <f>ROUND('Sheet 1'!E37, 3)</f>
